--- a/DataAnalysis/AdditionalModels/Discriminators/CS/0.05/NO_CLSDIV/res_scrimin=-1.csv.xlsx
+++ b/DataAnalysis/AdditionalModels/Discriminators/CS/0.05/NO_CLSDIV/res_scrimin=-1.csv.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\Discriminators\CI\0.3\NO_CLSDIV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\AdditionalModels\Discriminators\CS\0.05\NO_CLSDIV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43632259-0445-4238-992D-10535245A502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F971C04-5085-4025-BA9A-E0EA11ACDC9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0F214021-6FB1-40D5-9709-F0BEE25B15FC}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="37">
   <si>
     <t>Procedo per riga (prima riga, poi seconda riga, …)</t>
   </si>
@@ -129,6 +129,21 @@
   </si>
   <si>
     <t>Acc</t>
+  </si>
+  <si>
+    <t>Matrix</t>
+  </si>
+  <si>
+    <t>Class 0</t>
+  </si>
+  <si>
+    <t>Class 1</t>
+  </si>
+  <si>
+    <t>Class 2</t>
+  </si>
+  <si>
+    <t>CM</t>
   </si>
 </sst>
 </file>
@@ -997,7 +1012,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDEE7005-D29F-4A3A-8B33-A4338B8F6744}">
-  <dimension ref="A1:AL44"/>
+  <dimension ref="A1:AL47"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" customWidth="1"/>
@@ -1005,10 +1020,18 @@
   <sheetData>
     <row r="1" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1084,38 +1107,87 @@
       <c r="AD1" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="AF1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="2" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
+      <c r="A2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="1">
+        <v>74</v>
+      </c>
+      <c r="D2" s="1">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1">
+        <v>122</v>
+      </c>
       <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
+      <c r="G2" s="1">
+        <v>74</v>
+      </c>
+      <c r="H2" s="1">
+        <v>4</v>
+      </c>
+      <c r="I2" s="1">
+        <v>122</v>
+      </c>
+      <c r="J2" s="1">
+        <v>10</v>
+      </c>
+      <c r="K2" s="1">
+        <v>112</v>
+      </c>
+      <c r="L2" s="1">
+        <v>78</v>
+      </c>
+      <c r="M2" s="1">
+        <v>1</v>
+      </c>
+      <c r="N2" s="1">
+        <v>3</v>
+      </c>
+      <c r="O2" s="1">
+        <v>196</v>
+      </c>
       <c r="P2" s="1">
         <f>G2+K2+O2</f>
-        <v>0</v>
+        <v>382</v>
       </c>
       <c r="Q2" s="1">
         <f>G2+J2+M2</f>
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="R2" s="1">
         <f>H2+K2+N2</f>
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="S2" s="1">
         <f>I2+L2+O2</f>
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="T2" s="1">
         <v>200</v>
@@ -1126,29 +1198,29 @@
       <c r="V2" s="1">
         <v>200</v>
       </c>
-      <c r="W2" s="1" t="e">
+      <c r="W2" s="1">
         <f>G2/Q2</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X2" s="1" t="e">
+        <v>0.87058823529411766</v>
+      </c>
+      <c r="X2" s="1">
         <f>K2/R2</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Y2" s="1" t="e">
+        <v>0.94117647058823528</v>
+      </c>
+      <c r="Y2" s="1">
         <f>O2/S2</f>
-        <v>#DIV/0!</v>
+        <v>0.49494949494949497</v>
       </c>
       <c r="Z2" s="1">
         <f>G2/T2</f>
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="AA2" s="1">
         <f>K2/U2</f>
-        <v>0</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="AB2" s="1">
         <f>O2/V2</f>
-        <v>0</v>
+        <v>0.98</v>
       </c>
       <c r="AC2" s="1">
         <f>SUM(T2:V2)</f>
@@ -1156,121 +1228,240 @@
       </c>
       <c r="AD2" s="1">
         <f>P2/AC2</f>
+        <v>0.63666666666666671</v>
+      </c>
+      <c r="AF2">
+        <f>AVERAGE(W2:W11)</f>
+        <v>0.88885431072765031</v>
+      </c>
+      <c r="AG2">
+        <f>AVERAGE(X2:X11)</f>
+        <v>0.95139318709216047</v>
+      </c>
+      <c r="AH2">
+        <f>AVERAGE(Y2:Y11)</f>
+        <v>0.49970844487162924</v>
+      </c>
+      <c r="AI2">
+        <f>AVERAGE(Z2:Z11)</f>
+        <v>0.35849999999999999</v>
+      </c>
+      <c r="AJ2">
+        <f>AVERAGE(AA2:AA11)</f>
+        <v>0.58099999999999996</v>
+      </c>
+      <c r="AK2">
+        <f>AVERAGE(AB2:AB11)</f>
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="AL2">
+        <f>AVERAGE(AD2:AD11)</f>
+        <v>0.64383333333333337</v>
+      </c>
+    </row>
+    <row r="3" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="1">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1">
+        <v>112</v>
+      </c>
+      <c r="E3" s="1">
+        <v>78</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1">
+        <v>66</v>
+      </c>
+      <c r="H3" s="1">
+        <v>7</v>
+      </c>
+      <c r="I3" s="1">
+        <v>127</v>
+      </c>
+      <c r="J3" s="1">
+        <v>8</v>
+      </c>
+      <c r="K3" s="1">
+        <v>126</v>
+      </c>
+      <c r="L3" s="1">
+        <v>66</v>
+      </c>
+      <c r="M3" s="1">
         <v>0</v>
       </c>
-      <c r="AF2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AI2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="AJ2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="AK2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AL2" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
-      <c r="R3" s="1"/>
-      <c r="S3" s="1"/>
-      <c r="T3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="1"/>
-      <c r="W3" s="1"/>
-      <c r="X3" s="1"/>
-      <c r="Y3" s="1"/>
-      <c r="Z3" s="1"/>
-      <c r="AA3" s="1"/>
-      <c r="AB3" s="1"/>
-      <c r="AC3" s="1"/>
-      <c r="AD3" s="1"/>
-      <c r="AF3" t="e">
-        <f t="shared" ref="AF3:AK3" si="0">AVERAGE(W3:W11)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AG3" t="e">
+      <c r="N3" s="1">
+        <v>2</v>
+      </c>
+      <c r="O3" s="1">
+        <v>198</v>
+      </c>
+      <c r="P3" s="1">
+        <f t="shared" ref="P3:P11" si="0">G3+K3+O3</f>
+        <v>390</v>
+      </c>
+      <c r="Q3" s="1">
+        <f t="shared" ref="Q3:Q11" si="1">G3+J3+M3</f>
+        <v>74</v>
+      </c>
+      <c r="R3" s="1">
+        <f t="shared" ref="R3:R11" si="2">H3+K3+N3</f>
+        <v>135</v>
+      </c>
+      <c r="S3" s="1">
+        <f t="shared" ref="S3:S11" si="3">I3+L3+O3</f>
+        <v>391</v>
+      </c>
+      <c r="T3" s="1">
+        <v>200</v>
+      </c>
+      <c r="U3" s="1">
+        <v>200</v>
+      </c>
+      <c r="V3" s="1">
+        <v>200</v>
+      </c>
+      <c r="W3" s="1">
+        <f t="shared" ref="W3:W11" si="4">G3/Q3</f>
+        <v>0.89189189189189189</v>
+      </c>
+      <c r="X3" s="1">
+        <f t="shared" ref="X3:X11" si="5">K3/R3</f>
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="Y3" s="1">
+        <f t="shared" ref="Y3:Y11" si="6">O3/S3</f>
+        <v>0.50639386189258317</v>
+      </c>
+      <c r="Z3" s="1">
+        <f t="shared" ref="Z3:Z11" si="7">G3/T3</f>
+        <v>0.33</v>
+      </c>
+      <c r="AA3" s="1">
+        <f t="shared" ref="AA3:AA11" si="8">K3/U3</f>
+        <v>0.63</v>
+      </c>
+      <c r="AB3" s="1">
+        <f t="shared" ref="AB3:AB11" si="9">O3/V3</f>
+        <v>0.99</v>
+      </c>
+      <c r="AC3" s="1">
+        <f t="shared" ref="AC3:AC11" si="10">SUM(T3:V3)</f>
+        <v>600</v>
+      </c>
+      <c r="AD3" s="1">
+        <f t="shared" ref="AD3:AD11" si="11">P3/AC3</f>
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="1">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1">
+        <v>3</v>
+      </c>
+      <c r="E4" s="1">
+        <v>196</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1">
+        <v>72</v>
+      </c>
+      <c r="H4" s="1">
+        <v>6</v>
+      </c>
+      <c r="I4" s="1">
+        <v>122</v>
+      </c>
+      <c r="J4" s="1">
+        <v>8</v>
+      </c>
+      <c r="K4" s="1">
+        <v>116</v>
+      </c>
+      <c r="L4" s="1">
+        <v>76</v>
+      </c>
+      <c r="M4" s="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1">
+        <v>1</v>
+      </c>
+      <c r="O4" s="1">
+        <v>199</v>
+      </c>
+      <c r="P4" s="1">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AH3" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI3" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AJ3" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AK3" t="e">
-        <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL3" t="e">
-        <f>AVERAGE(AD3:AD11)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="1"/>
-      <c r="W4" s="1"/>
-      <c r="X4" s="1"/>
-      <c r="Y4" s="1"/>
-      <c r="Z4" s="1"/>
-      <c r="AA4" s="1"/>
-      <c r="AB4" s="1"/>
-      <c r="AC4" s="1"/>
-      <c r="AD4" s="1"/>
+        <v>387</v>
+      </c>
+      <c r="Q4" s="1">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="R4" s="1">
+        <f t="shared" si="2"/>
+        <v>123</v>
+      </c>
+      <c r="S4" s="1">
+        <f t="shared" si="3"/>
+        <v>397</v>
+      </c>
+      <c r="T4" s="1">
+        <v>200</v>
+      </c>
+      <c r="U4" s="1">
+        <v>200</v>
+      </c>
+      <c r="V4" s="1">
+        <v>200</v>
+      </c>
+      <c r="W4" s="1">
+        <f t="shared" si="4"/>
+        <v>0.9</v>
+      </c>
+      <c r="X4" s="1">
+        <f t="shared" si="5"/>
+        <v>0.94308943089430897</v>
+      </c>
+      <c r="Y4" s="1">
+        <f t="shared" si="6"/>
+        <v>0.50125944584382875</v>
+      </c>
+      <c r="Z4" s="1">
+        <f t="shared" si="7"/>
+        <v>0.36</v>
+      </c>
+      <c r="AA4" s="1">
+        <f t="shared" si="8"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="AB4" s="1">
+        <f t="shared" si="9"/>
+        <v>0.995</v>
+      </c>
+      <c r="AC4" s="1">
+        <f t="shared" si="10"/>
+        <v>600</v>
+      </c>
+      <c r="AD4" s="1">
+        <f t="shared" si="11"/>
+        <v>0.64500000000000002</v>
+      </c>
     </row>
     <row r="5" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
@@ -1279,158 +1470,496 @@
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
-      <c r="R5" s="1"/>
-      <c r="S5" s="1"/>
-      <c r="T5" s="1"/>
-      <c r="U5" s="1"/>
-      <c r="V5" s="1"/>
-      <c r="W5" s="1"/>
-      <c r="X5" s="1"/>
-      <c r="Y5" s="1"/>
-      <c r="Z5" s="1"/>
-      <c r="AA5" s="1"/>
-      <c r="AB5" s="1"/>
-      <c r="AC5" s="1"/>
-      <c r="AD5" s="1"/>
+      <c r="G5" s="1">
+        <v>81</v>
+      </c>
+      <c r="H5" s="1">
+        <v>3</v>
+      </c>
+      <c r="I5" s="1">
+        <v>116</v>
+      </c>
+      <c r="J5" s="1">
+        <v>5</v>
+      </c>
+      <c r="K5" s="1">
+        <v>118</v>
+      </c>
+      <c r="L5" s="1">
+        <v>77</v>
+      </c>
+      <c r="M5" s="1">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1">
+        <v>200</v>
+      </c>
+      <c r="P5" s="1">
+        <f t="shared" si="0"/>
+        <v>399</v>
+      </c>
+      <c r="Q5" s="1">
+        <f t="shared" si="1"/>
+        <v>86</v>
+      </c>
+      <c r="R5" s="1">
+        <f t="shared" si="2"/>
+        <v>121</v>
+      </c>
+      <c r="S5" s="1">
+        <f t="shared" si="3"/>
+        <v>393</v>
+      </c>
+      <c r="T5" s="1">
+        <v>200</v>
+      </c>
+      <c r="U5" s="1">
+        <v>200</v>
+      </c>
+      <c r="V5" s="1">
+        <v>200</v>
+      </c>
+      <c r="W5" s="1">
+        <f t="shared" si="4"/>
+        <v>0.94186046511627908</v>
+      </c>
+      <c r="X5" s="1">
+        <f t="shared" si="5"/>
+        <v>0.97520661157024791</v>
+      </c>
+      <c r="Y5" s="1">
+        <f t="shared" si="6"/>
+        <v>0.5089058524173028</v>
+      </c>
+      <c r="Z5" s="1">
+        <f t="shared" si="7"/>
+        <v>0.40500000000000003</v>
+      </c>
+      <c r="AA5" s="1">
+        <f t="shared" si="8"/>
+        <v>0.59</v>
+      </c>
+      <c r="AB5" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="AC5" s="1">
+        <f t="shared" si="10"/>
+        <v>600</v>
+      </c>
+      <c r="AD5" s="1">
+        <f t="shared" si="11"/>
+        <v>0.66500000000000004</v>
+      </c>
     </row>
     <row r="6" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
+      <c r="B6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="R6" s="1"/>
-      <c r="S6" s="1"/>
-      <c r="T6" s="1"/>
-      <c r="U6" s="1"/>
-      <c r="V6" s="1"/>
-      <c r="W6" s="1"/>
-      <c r="X6" s="1"/>
-      <c r="Y6" s="1"/>
-      <c r="Z6" s="1"/>
-      <c r="AA6" s="1"/>
-      <c r="AB6" s="1"/>
-      <c r="AC6" s="1"/>
-      <c r="AD6" s="1"/>
+      <c r="G6" s="1">
+        <v>65</v>
+      </c>
+      <c r="H6" s="1">
+        <v>2</v>
+      </c>
+      <c r="I6" s="1">
+        <v>133</v>
+      </c>
+      <c r="J6" s="1">
+        <v>9</v>
+      </c>
+      <c r="K6" s="1">
+        <v>121</v>
+      </c>
+      <c r="L6" s="1">
+        <v>70</v>
+      </c>
+      <c r="M6" s="1">
+        <v>2</v>
+      </c>
+      <c r="N6" s="1">
+        <v>2</v>
+      </c>
+      <c r="O6" s="1">
+        <v>196</v>
+      </c>
+      <c r="P6" s="1">
+        <f t="shared" si="0"/>
+        <v>382</v>
+      </c>
+      <c r="Q6" s="1">
+        <f t="shared" si="1"/>
+        <v>76</v>
+      </c>
+      <c r="R6" s="1">
+        <f t="shared" si="2"/>
+        <v>125</v>
+      </c>
+      <c r="S6" s="1">
+        <f t="shared" si="3"/>
+        <v>399</v>
+      </c>
+      <c r="T6" s="1">
+        <v>200</v>
+      </c>
+      <c r="U6" s="1">
+        <v>200</v>
+      </c>
+      <c r="V6" s="1">
+        <v>200</v>
+      </c>
+      <c r="W6" s="1">
+        <f t="shared" si="4"/>
+        <v>0.85526315789473684</v>
+      </c>
+      <c r="X6" s="1">
+        <f t="shared" si="5"/>
+        <v>0.96799999999999997</v>
+      </c>
+      <c r="Y6" s="1">
+        <f t="shared" si="6"/>
+        <v>0.49122807017543857</v>
+      </c>
+      <c r="Z6" s="1">
+        <f t="shared" si="7"/>
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="AA6" s="1">
+        <f t="shared" si="8"/>
+        <v>0.60499999999999998</v>
+      </c>
+      <c r="AB6" s="1">
+        <f t="shared" si="9"/>
+        <v>0.98</v>
+      </c>
+      <c r="AC6" s="1">
+        <f t="shared" si="10"/>
+        <v>600</v>
+      </c>
+      <c r="AD6" s="1">
+        <f t="shared" si="11"/>
+        <v>0.63666666666666671</v>
+      </c>
     </row>
     <row r="7" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
+      <c r="A7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="1">
+        <v>66</v>
+      </c>
+      <c r="D7" s="1">
+        <v>7</v>
+      </c>
+      <c r="E7" s="1">
+        <v>127</v>
+      </c>
       <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
-      <c r="R7" s="1"/>
-      <c r="S7" s="1"/>
-      <c r="T7" s="1"/>
-      <c r="U7" s="1"/>
-      <c r="V7" s="1"/>
-      <c r="W7" s="1"/>
-      <c r="X7" s="1"/>
-      <c r="Y7" s="1"/>
-      <c r="Z7" s="1"/>
-      <c r="AA7" s="1"/>
-      <c r="AB7" s="1"/>
-      <c r="AC7" s="1"/>
-      <c r="AD7" s="1"/>
+      <c r="G7" s="1">
+        <v>76</v>
+      </c>
+      <c r="H7" s="1">
+        <v>5</v>
+      </c>
+      <c r="I7" s="1">
+        <v>119</v>
+      </c>
+      <c r="J7" s="1">
+        <v>11</v>
+      </c>
+      <c r="K7" s="1">
+        <v>112</v>
+      </c>
+      <c r="L7" s="1">
+        <v>77</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1">
+        <v>200</v>
+      </c>
+      <c r="P7" s="1">
+        <f t="shared" si="0"/>
+        <v>388</v>
+      </c>
+      <c r="Q7" s="1">
+        <f t="shared" si="1"/>
+        <v>87</v>
+      </c>
+      <c r="R7" s="1">
+        <f t="shared" si="2"/>
+        <v>117</v>
+      </c>
+      <c r="S7" s="1">
+        <f t="shared" si="3"/>
+        <v>396</v>
+      </c>
+      <c r="T7" s="1">
+        <v>200</v>
+      </c>
+      <c r="U7" s="1">
+        <v>200</v>
+      </c>
+      <c r="V7" s="1">
+        <v>200</v>
+      </c>
+      <c r="W7" s="1">
+        <f t="shared" si="4"/>
+        <v>0.87356321839080464</v>
+      </c>
+      <c r="X7" s="1">
+        <f t="shared" si="5"/>
+        <v>0.95726495726495731</v>
+      </c>
+      <c r="Y7" s="1">
+        <f t="shared" si="6"/>
+        <v>0.50505050505050508</v>
+      </c>
+      <c r="Z7" s="1">
+        <f t="shared" si="7"/>
+        <v>0.38</v>
+      </c>
+      <c r="AA7" s="1">
+        <f t="shared" si="8"/>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="AB7" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="AC7" s="1">
+        <f t="shared" si="10"/>
+        <v>600</v>
+      </c>
+      <c r="AD7" s="1">
+        <f t="shared" si="11"/>
+        <v>0.64666666666666661</v>
+      </c>
     </row>
     <row r="8" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
+      <c r="A8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="1">
+        <v>8</v>
+      </c>
+      <c r="D8" s="1">
+        <v>126</v>
+      </c>
+      <c r="E8" s="1">
+        <v>66</v>
+      </c>
       <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-      <c r="T8" s="1"/>
-      <c r="U8" s="1"/>
-      <c r="V8" s="1"/>
-      <c r="W8" s="1"/>
-      <c r="X8" s="1"/>
-      <c r="Y8" s="1"/>
-      <c r="Z8" s="1"/>
-      <c r="AA8" s="1"/>
-      <c r="AB8" s="1"/>
-      <c r="AC8" s="1"/>
-      <c r="AD8" s="1"/>
+      <c r="G8" s="1">
+        <v>80</v>
+      </c>
+      <c r="H8" s="1">
+        <v>3</v>
+      </c>
+      <c r="I8" s="1">
+        <v>117</v>
+      </c>
+      <c r="J8" s="1">
+        <v>4</v>
+      </c>
+      <c r="K8" s="1">
+        <v>130</v>
+      </c>
+      <c r="L8" s="1">
+        <v>66</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0</v>
+      </c>
+      <c r="O8" s="1">
+        <v>200</v>
+      </c>
+      <c r="P8" s="1">
+        <f t="shared" si="0"/>
+        <v>410</v>
+      </c>
+      <c r="Q8" s="1">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
+      <c r="R8" s="1">
+        <f t="shared" si="2"/>
+        <v>133</v>
+      </c>
+      <c r="S8" s="1">
+        <f t="shared" si="3"/>
+        <v>383</v>
+      </c>
+      <c r="T8" s="1">
+        <v>200</v>
+      </c>
+      <c r="U8" s="1">
+        <v>200</v>
+      </c>
+      <c r="V8" s="1">
+        <v>200</v>
+      </c>
+      <c r="W8" s="1">
+        <f t="shared" si="4"/>
+        <v>0.95238095238095233</v>
+      </c>
+      <c r="X8" s="1">
+        <f t="shared" si="5"/>
+        <v>0.97744360902255634</v>
+      </c>
+      <c r="Y8" s="1">
+        <f t="shared" si="6"/>
+        <v>0.52219321148825071</v>
+      </c>
+      <c r="Z8" s="1">
+        <f t="shared" si="7"/>
+        <v>0.4</v>
+      </c>
+      <c r="AA8" s="1">
+        <f t="shared" si="8"/>
+        <v>0.65</v>
+      </c>
+      <c r="AB8" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="AC8" s="1">
+        <f t="shared" si="10"/>
+        <v>600</v>
+      </c>
+      <c r="AD8" s="1">
+        <f t="shared" si="11"/>
+        <v>0.68333333333333335</v>
+      </c>
     </row>
     <row r="9" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
+      <c r="A9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="1">
+        <v>0</v>
+      </c>
+      <c r="D9" s="1">
+        <v>2</v>
+      </c>
+      <c r="E9" s="1">
+        <v>198</v>
+      </c>
       <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-      <c r="Q9" s="1"/>
-      <c r="R9" s="1"/>
-      <c r="S9" s="1"/>
-      <c r="T9" s="1"/>
-      <c r="U9" s="1"/>
-      <c r="V9" s="1"/>
-      <c r="W9" s="1"/>
-      <c r="X9" s="1"/>
-      <c r="Y9" s="1"/>
-      <c r="Z9" s="1"/>
-      <c r="AA9" s="1"/>
-      <c r="AB9" s="1"/>
-      <c r="AC9" s="1"/>
-      <c r="AD9" s="1"/>
+      <c r="G9" s="1">
+        <v>68</v>
+      </c>
+      <c r="H9" s="1">
+        <v>6</v>
+      </c>
+      <c r="I9" s="1">
+        <v>126</v>
+      </c>
+      <c r="J9" s="1">
+        <v>15</v>
+      </c>
+      <c r="K9" s="1">
+        <v>98</v>
+      </c>
+      <c r="L9" s="1">
+        <v>87</v>
+      </c>
+      <c r="M9" s="1">
+        <v>2</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0</v>
+      </c>
+      <c r="O9" s="1">
+        <v>198</v>
+      </c>
+      <c r="P9" s="1">
+        <f t="shared" si="0"/>
+        <v>364</v>
+      </c>
+      <c r="Q9" s="1">
+        <f t="shared" si="1"/>
+        <v>85</v>
+      </c>
+      <c r="R9" s="1">
+        <f t="shared" si="2"/>
+        <v>104</v>
+      </c>
+      <c r="S9" s="1">
+        <f t="shared" si="3"/>
+        <v>411</v>
+      </c>
+      <c r="T9" s="1">
+        <v>200</v>
+      </c>
+      <c r="U9" s="1">
+        <v>200</v>
+      </c>
+      <c r="V9" s="1">
+        <v>200</v>
+      </c>
+      <c r="W9" s="1">
+        <f t="shared" si="4"/>
+        <v>0.8</v>
+      </c>
+      <c r="X9" s="1">
+        <f t="shared" si="5"/>
+        <v>0.94230769230769229</v>
+      </c>
+      <c r="Y9" s="1">
+        <f t="shared" si="6"/>
+        <v>0.48175182481751827</v>
+      </c>
+      <c r="Z9" s="1">
+        <f t="shared" si="7"/>
+        <v>0.34</v>
+      </c>
+      <c r="AA9" s="1">
+        <f t="shared" si="8"/>
+        <v>0.49</v>
+      </c>
+      <c r="AB9" s="1">
+        <f t="shared" si="9"/>
+        <v>0.99</v>
+      </c>
+      <c r="AC9" s="1">
+        <f t="shared" si="10"/>
+        <v>600</v>
+      </c>
+      <c r="AD9" s="1">
+        <f t="shared" si="11"/>
+        <v>0.60666666666666669</v>
+      </c>
     </row>
     <row r="10" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
@@ -1439,69 +1968,207 @@
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-      <c r="Q10" s="1"/>
-      <c r="R10" s="1"/>
-      <c r="S10" s="1"/>
-      <c r="T10" s="1"/>
-      <c r="U10" s="1"/>
-      <c r="V10" s="1"/>
-      <c r="W10" s="1"/>
-      <c r="X10" s="1"/>
-      <c r="Y10" s="1"/>
-      <c r="Z10" s="1"/>
-      <c r="AA10" s="1"/>
-      <c r="AB10" s="1"/>
-      <c r="AC10" s="1"/>
-      <c r="AD10" s="1"/>
+      <c r="G10" s="1">
+        <v>69</v>
+      </c>
+      <c r="H10" s="1">
+        <v>6</v>
+      </c>
+      <c r="I10" s="1">
+        <v>125</v>
+      </c>
+      <c r="J10" s="1">
+        <v>7</v>
+      </c>
+      <c r="K10" s="1">
+        <v>120</v>
+      </c>
+      <c r="L10" s="1">
+        <v>73</v>
+      </c>
+      <c r="M10" s="1">
+        <v>3</v>
+      </c>
+      <c r="N10" s="1">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1">
+        <v>197</v>
+      </c>
+      <c r="P10" s="1">
+        <f t="shared" si="0"/>
+        <v>386</v>
+      </c>
+      <c r="Q10" s="1">
+        <f t="shared" si="1"/>
+        <v>79</v>
+      </c>
+      <c r="R10" s="1">
+        <f t="shared" si="2"/>
+        <v>126</v>
+      </c>
+      <c r="S10" s="1">
+        <f t="shared" si="3"/>
+        <v>395</v>
+      </c>
+      <c r="T10" s="1">
+        <v>200</v>
+      </c>
+      <c r="U10" s="1">
+        <v>200</v>
+      </c>
+      <c r="V10" s="1">
+        <v>200</v>
+      </c>
+      <c r="W10" s="1">
+        <f t="shared" si="4"/>
+        <v>0.87341772151898733</v>
+      </c>
+      <c r="X10" s="1">
+        <f t="shared" si="5"/>
+        <v>0.95238095238095233</v>
+      </c>
+      <c r="Y10" s="1">
+        <f t="shared" si="6"/>
+        <v>0.49873417721518987</v>
+      </c>
+      <c r="Z10" s="1">
+        <f t="shared" si="7"/>
+        <v>0.34499999999999997</v>
+      </c>
+      <c r="AA10" s="1">
+        <f t="shared" si="8"/>
+        <v>0.6</v>
+      </c>
+      <c r="AB10" s="1">
+        <f t="shared" si="9"/>
+        <v>0.98499999999999999</v>
+      </c>
+      <c r="AC10" s="1">
+        <f t="shared" si="10"/>
+        <v>600</v>
+      </c>
+      <c r="AD10" s="1">
+        <f t="shared" si="11"/>
+        <v>0.64333333333333331</v>
+      </c>
     </row>
     <row r="11" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
+      <c r="B11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-      <c r="U11" s="1"/>
-      <c r="V11" s="1"/>
-      <c r="W11" s="1"/>
-      <c r="X11" s="1"/>
-      <c r="Y11" s="1"/>
-      <c r="Z11" s="1"/>
-      <c r="AA11" s="1"/>
-      <c r="AB11" s="1"/>
-      <c r="AC11" s="1"/>
-      <c r="AD11" s="1"/>
+      <c r="G11" s="1">
+        <v>66</v>
+      </c>
+      <c r="H11" s="1">
+        <v>9</v>
+      </c>
+      <c r="I11" s="1">
+        <v>125</v>
+      </c>
+      <c r="J11" s="1">
+        <v>5</v>
+      </c>
+      <c r="K11">
+        <v>109</v>
+      </c>
+      <c r="L11">
+        <v>86</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>200</v>
+      </c>
+      <c r="P11" s="1">
+        <f t="shared" si="0"/>
+        <v>375</v>
+      </c>
+      <c r="Q11" s="1">
+        <f t="shared" si="1"/>
+        <v>71</v>
+      </c>
+      <c r="R11" s="1">
+        <f t="shared" si="2"/>
+        <v>118</v>
+      </c>
+      <c r="S11" s="1">
+        <f t="shared" si="3"/>
+        <v>411</v>
+      </c>
+      <c r="T11" s="1">
+        <v>200</v>
+      </c>
+      <c r="U11" s="1">
+        <v>200</v>
+      </c>
+      <c r="V11" s="1">
+        <v>200</v>
+      </c>
+      <c r="W11" s="1">
+        <f t="shared" si="4"/>
+        <v>0.92957746478873238</v>
+      </c>
+      <c r="X11" s="1">
+        <f t="shared" si="5"/>
+        <v>0.92372881355932202</v>
+      </c>
+      <c r="Y11" s="1">
+        <f t="shared" si="6"/>
+        <v>0.48661800486618007</v>
+      </c>
+      <c r="Z11" s="1">
+        <f t="shared" si="7"/>
+        <v>0.33</v>
+      </c>
+      <c r="AA11" s="1">
+        <f t="shared" si="8"/>
+        <v>0.54500000000000004</v>
+      </c>
+      <c r="AB11" s="1">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="AC11" s="1">
+        <f t="shared" si="10"/>
+        <v>600</v>
+      </c>
+      <c r="AD11" s="1">
+        <f t="shared" si="11"/>
+        <v>0.625</v>
+      </c>
     </row>
     <row r="12" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
+      <c r="A12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="1">
+        <v>72</v>
+      </c>
+      <c r="D12" s="1">
+        <v>6</v>
+      </c>
+      <c r="E12" s="1">
+        <v>122</v>
+      </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -1529,11 +2196,21 @@
       <c r="AD12" s="1"/>
     </row>
     <row r="13" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
+      <c r="A13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="1">
+        <v>8</v>
+      </c>
+      <c r="D13" s="1">
+        <v>116</v>
+      </c>
+      <c r="E13" s="1">
+        <v>76</v>
+      </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
@@ -1561,11 +2238,21 @@
       <c r="AD13" s="1"/>
     </row>
     <row r="14" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
+      <c r="A14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="1">
+        <v>0</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1">
+        <v>199</v>
+      </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
@@ -1626,10 +2313,18 @@
     </row>
     <row r="16" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
+      <c r="B16" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
@@ -1657,11 +2352,21 @@
       <c r="AD16" s="1"/>
     </row>
     <row r="17" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
+      <c r="A17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="1">
+        <v>81</v>
+      </c>
+      <c r="D17" s="1">
+        <v>3</v>
+      </c>
+      <c r="E17" s="1">
+        <v>116</v>
+      </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
@@ -1689,11 +2394,21 @@
       <c r="AD17" s="1"/>
     </row>
     <row r="18" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
+      <c r="A18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="1">
+        <v>5</v>
+      </c>
+      <c r="D18" s="1">
+        <v>118</v>
+      </c>
+      <c r="E18" s="1">
+        <v>77</v>
+      </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
@@ -1721,11 +2436,21 @@
       <c r="AD18" s="1"/>
     </row>
     <row r="19" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
+      <c r="A19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="1">
+        <v>0</v>
+      </c>
+      <c r="D19" s="1">
+        <v>0</v>
+      </c>
+      <c r="E19" s="1">
+        <v>200</v>
+      </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
@@ -1754,10 +2479,18 @@
     </row>
     <row r="20" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
+      <c r="B20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
@@ -1785,11 +2518,21 @@
       <c r="AD20" s="1"/>
     </row>
     <row r="21" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
+      <c r="A21" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="1">
+        <v>65</v>
+      </c>
+      <c r="D21" s="1">
+        <v>2</v>
+      </c>
+      <c r="E21" s="1">
+        <v>133</v>
+      </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
@@ -1817,11 +2560,21 @@
       <c r="AD21" s="1"/>
     </row>
     <row r="22" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
+      <c r="A22" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="1">
+        <v>9</v>
+      </c>
+      <c r="D22" s="1">
+        <v>121</v>
+      </c>
+      <c r="E22" s="1">
+        <v>70</v>
+      </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
@@ -1849,11 +2602,21 @@
       <c r="AD22" s="1"/>
     </row>
     <row r="23" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
+      <c r="A23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="1">
+        <v>2</v>
+      </c>
+      <c r="D23" s="1">
+        <v>2</v>
+      </c>
+      <c r="E23" s="1">
+        <v>196</v>
+      </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
@@ -1914,10 +2677,18 @@
     </row>
     <row r="25" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
+      <c r="B25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
@@ -1945,11 +2716,21 @@
       <c r="AD25" s="1"/>
     </row>
     <row r="26" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="1">
+        <v>76</v>
+      </c>
+      <c r="D26" s="1">
+        <v>5</v>
+      </c>
+      <c r="E26" s="1">
+        <v>119</v>
+      </c>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
@@ -1977,11 +2758,21 @@
       <c r="AD26" s="1"/>
     </row>
     <row r="27" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="1">
+        <v>11</v>
+      </c>
+      <c r="D27" s="1">
+        <v>112</v>
+      </c>
+      <c r="E27" s="1">
+        <v>77</v>
+      </c>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
@@ -2009,11 +2800,21 @@
       <c r="AD27" s="1"/>
     </row>
     <row r="28" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C28" s="1">
+        <v>0</v>
+      </c>
+      <c r="D28" s="1">
+        <v>0</v>
+      </c>
+      <c r="E28" s="1">
+        <v>200</v>
+      </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
@@ -2074,10 +2875,18 @@
     </row>
     <row r="30" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
+      <c r="B30" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
@@ -2105,11 +2914,21 @@
       <c r="AD30" s="1"/>
     </row>
     <row r="31" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
+      <c r="A31" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="1">
+        <v>80</v>
+      </c>
+      <c r="D31" s="1">
+        <v>3</v>
+      </c>
+      <c r="E31" s="1">
+        <v>117</v>
+      </c>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
@@ -2137,11 +2956,21 @@
       <c r="AD31" s="1"/>
     </row>
     <row r="32" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
+      <c r="A32" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" s="1">
+        <v>4</v>
+      </c>
+      <c r="D32" s="1">
+        <v>130</v>
+      </c>
+      <c r="E32" s="1">
+        <v>66</v>
+      </c>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
@@ -2169,11 +2998,21 @@
       <c r="AD32" s="1"/>
     </row>
     <row r="33" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
+      <c r="A33" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" s="1">
+        <v>0</v>
+      </c>
+      <c r="D33" s="1">
+        <v>0</v>
+      </c>
+      <c r="E33" s="1">
+        <v>200</v>
+      </c>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
@@ -2234,10 +3073,18 @@
     </row>
     <row r="35" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
+      <c r="B35" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
@@ -2265,11 +3112,21 @@
       <c r="AD35" s="1"/>
     </row>
     <row r="36" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
+      <c r="A36" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" s="1">
+        <v>68</v>
+      </c>
+      <c r="D36" s="1">
+        <v>6</v>
+      </c>
+      <c r="E36" s="1">
+        <v>126</v>
+      </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
@@ -2297,11 +3154,21 @@
       <c r="AD36" s="1"/>
     </row>
     <row r="37" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
+      <c r="A37" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C37" s="1">
+        <v>15</v>
+      </c>
+      <c r="D37" s="1">
+        <v>98</v>
+      </c>
+      <c r="E37" s="1">
+        <v>87</v>
+      </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
@@ -2329,11 +3196,21 @@
       <c r="AD37" s="1"/>
     </row>
     <row r="38" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
+      <c r="A38" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C38" s="1">
+        <v>2</v>
+      </c>
+      <c r="D38" s="1">
+        <v>0</v>
+      </c>
+      <c r="E38" s="1">
+        <v>198</v>
+      </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
@@ -2362,10 +3239,18 @@
     </row>
     <row r="39" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
+      <c r="B39" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
@@ -2393,11 +3278,21 @@
       <c r="AD39" s="1"/>
     </row>
     <row r="40" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
+      <c r="A40" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C40" s="1">
+        <v>69</v>
+      </c>
+      <c r="D40" s="1">
+        <v>6</v>
+      </c>
+      <c r="E40" s="1">
+        <v>125</v>
+      </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
@@ -2425,11 +3320,21 @@
       <c r="AD40" s="1"/>
     </row>
     <row r="41" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
+      <c r="A41" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C41" s="1">
+        <v>7</v>
+      </c>
+      <c r="D41" s="1">
+        <v>120</v>
+      </c>
+      <c r="E41" s="1">
+        <v>73</v>
+      </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
@@ -2457,11 +3362,21 @@
       <c r="AD41" s="1"/>
     </row>
     <row r="42" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
+      <c r="A42" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="1">
+        <v>3</v>
+      </c>
+      <c r="D42" s="1">
+        <v>0</v>
+      </c>
+      <c r="E42" s="1">
+        <v>197</v>
+      </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
@@ -2522,10 +3437,18 @@
     </row>
     <row r="44" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
+      <c r="B44" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
@@ -2552,6 +3475,57 @@
       <c r="AC44" s="1"/>
       <c r="AD44" s="1"/>
     </row>
+    <row r="45" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>33</v>
+      </c>
+      <c r="B45" t="s">
+        <v>36</v>
+      </c>
+      <c r="C45">
+        <v>66</v>
+      </c>
+      <c r="D45">
+        <v>9</v>
+      </c>
+      <c r="E45">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="46" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>34</v>
+      </c>
+      <c r="B46" t="s">
+        <v>36</v>
+      </c>
+      <c r="C46">
+        <v>5</v>
+      </c>
+      <c r="D46">
+        <v>109</v>
+      </c>
+      <c r="E46">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="47" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>35</v>
+      </c>
+      <c r="B47" t="s">
+        <v>36</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>0</v>
+      </c>
+      <c r="E47">
+        <v>200</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
